--- a/Preliminary Data/two forces micro perturbed (15 tirals)(tapered and cylindrical)/Validation(1.5)(3tendon).xlsx
+++ b/Preliminary Data/two forces micro perturbed (15 tirals)(tapered and cylindrical)/Validation(1.5)(3tendon).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Raw Data/two forces micro perturbed (15 tirals)(tapered and cylindrical)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Preliminary Data/two forces micro perturbed (15 tirals)(tapered and cylindrical)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4034" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E48F22E1-F31A-4947-B8D0-A7AA3DB9ABD6}"/>
+  <xr:revisionPtr revIDLastSave="4045" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3867DB4-B38C-4215-B2A7-989A297FB26D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximal Validation" sheetId="12" r:id="rId1"/>
@@ -2545,7 +2545,7 @@
     </row>
     <row r="22" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R22">
-        <f t="shared" ref="R22:R39" si="10">SQRT(SUMXMY2(R4:W4,R$19:W$19))</f>
+        <f t="shared" ref="R22:R35" si="10">SQRT(SUMXMY2(R4:W4,R$19:W$19))</f>
         <v>0.63214672593098142</v>
       </c>
       <c r="T22">
@@ -9588,6 +9588,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048D6981-73D2-4F8C-88D7-D5FA77AC2EB0}">
   <dimension ref="A1:M54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="40" t="s">
@@ -9647,2290 +9650,1480 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.34101566672325101</v>
+        <v>-9.2765869339927998E-4</v>
       </c>
       <c r="B3">
-        <v>0.290946185588837</v>
+        <v>-1.33946887217462E-5</v>
       </c>
       <c r="C3">
-        <v>-0.186183482408524</v>
+        <v>-9.8100444301962896E-4</v>
       </c>
       <c r="D3">
-        <v>-3.2525759190321003E-2</v>
+        <v>2.88837986772705E-6</v>
       </c>
       <c r="E3">
-        <v>8.4817789494991302E-2</v>
+        <v>-1.88465310202446E-5</v>
       </c>
       <c r="F3" s="4">
-        <v>3.3966472838073999E-3</v>
+        <v>-1.60878016686183E-6</v>
       </c>
       <c r="H3">
         <f>$F3</f>
-        <v>3.3966472838073999E-3</v>
+        <v>-1.60878016686183E-6</v>
       </c>
       <c r="I3">
         <f>-1*$E3</f>
-        <v>-8.4817789494991302E-2</v>
+        <v>1.88465310202446E-5</v>
       </c>
       <c r="J3">
         <f>$D3</f>
-        <v>-3.2525759190321003E-2</v>
+        <v>2.88837986772705E-6</v>
       </c>
       <c r="K3">
         <f>$C3</f>
-        <v>-0.186183482408524</v>
+        <v>-9.8100444301962896E-4</v>
       </c>
       <c r="L3">
         <f>-1*$B3</f>
-        <v>-0.290946185588837</v>
+        <v>1.33946887217462E-5</v>
       </c>
       <c r="M3">
         <f>$A3</f>
-        <v>0.34101566672325101</v>
+        <v>-9.2765869339927998E-4</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.30814045667648299</v>
+        <v>0.397724568843842</v>
       </c>
       <c r="B4">
-        <v>0.31568014621734602</v>
+        <v>-1.5018563717603701E-3</v>
       </c>
       <c r="C4">
-        <v>-0.16215063631534599</v>
+        <v>-0.26717236638069197</v>
       </c>
       <c r="D4">
-        <v>-3.5355295985937098E-2</v>
+        <v>-2.2936267778277401E-3</v>
       </c>
       <c r="E4">
-        <v>7.6770626008510603E-2</v>
+        <v>0.12928463518619501</v>
       </c>
       <c r="F4">
-        <v>4.7846524976193896E-3</v>
+        <v>-3.0997174326330402E-4</v>
       </c>
       <c r="H4">
         <f t="shared" ref="H4:H54" si="0">$F4</f>
-        <v>4.7846524976193896E-3</v>
+        <v>-3.0997174326330402E-4</v>
       </c>
       <c r="I4">
         <f t="shared" ref="I4:I54" si="1">-1*$E4</f>
-        <v>-7.6770626008510603E-2</v>
+        <v>-0.12928463518619501</v>
       </c>
       <c r="J4">
         <f t="shared" ref="J4:J54" si="2">$D4</f>
-        <v>-3.5355295985937098E-2</v>
+        <v>-2.2936267778277401E-3</v>
       </c>
       <c r="K4">
         <f t="shared" ref="K4:K54" si="3">$C4</f>
-        <v>-0.16215063631534599</v>
+        <v>-0.26717236638069197</v>
       </c>
       <c r="L4">
         <f t="shared" ref="L4:L54" si="4">-1*$B4</f>
-        <v>-0.31568014621734602</v>
+        <v>1.5018563717603701E-3</v>
       </c>
       <c r="M4">
         <f t="shared" ref="M4:M54" si="5">$A4</f>
-        <v>0.30814045667648299</v>
+        <v>0.397724568843842</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0.30544507503509499</v>
+        <v>0.80131876468658403</v>
       </c>
       <c r="B5">
-        <v>0.26379287242889399</v>
+        <v>-2.6175640523433698E-3</v>
       </c>
       <c r="C5">
-        <v>-0.15830263495445299</v>
+        <v>-0.55141580104827903</v>
       </c>
       <c r="D5">
-        <v>-2.92263831943274E-2</v>
+        <v>-5.1040532998740699E-3</v>
       </c>
       <c r="E5">
-        <v>7.5815342366695404E-2</v>
+        <v>0.26506674289703402</v>
       </c>
       <c r="F5">
-        <v>1.75101147033274E-3</v>
+        <v>-1.31723959930241E-3</v>
       </c>
       <c r="H5">
         <f t="shared" si="0"/>
-        <v>1.75101147033274E-3</v>
+        <v>-1.31723959930241E-3</v>
       </c>
       <c r="I5">
         <f t="shared" si="1"/>
-        <v>-7.5815342366695404E-2</v>
+        <v>-0.26506674289703402</v>
       </c>
       <c r="J5">
         <f t="shared" si="2"/>
-        <v>-2.92263831943274E-2</v>
+        <v>-5.1040532998740699E-3</v>
       </c>
       <c r="K5">
         <f t="shared" si="3"/>
-        <v>-0.15830263495445299</v>
+        <v>-0.55141580104827903</v>
       </c>
       <c r="L5">
         <f t="shared" si="4"/>
-        <v>-0.26379287242889399</v>
+        <v>2.6175640523433698E-3</v>
       </c>
       <c r="M5">
         <f t="shared" si="5"/>
-        <v>0.30544507503509499</v>
+        <v>0.80131876468658403</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.37134739756584201</v>
+        <v>0.96414262056350697</v>
       </c>
       <c r="B6">
-        <v>0.286252111196518</v>
+        <v>-3.28068062663078E-3</v>
       </c>
       <c r="C6">
-        <v>-0.190847843885422</v>
+        <v>-0.67402482032775901</v>
       </c>
       <c r="D6">
-        <v>-3.1735785305500003E-2</v>
+        <v>-6.2346826307475602E-3</v>
       </c>
       <c r="E6">
-        <v>9.1100767254829407E-2</v>
+        <v>0.31844446063041698</v>
       </c>
       <c r="F6">
-        <v>3.5732281394302802E-3</v>
+        <v>-1.7683464102447E-3</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>3.5732281394302802E-3</v>
+        <v>-1.7683464102447E-3</v>
       </c>
       <c r="I6">
         <f t="shared" si="1"/>
-        <v>-9.1100767254829407E-2</v>
+        <v>-0.31844446063041698</v>
       </c>
       <c r="J6">
         <f t="shared" si="2"/>
-        <v>-3.1735785305500003E-2</v>
+        <v>-6.2346826307475602E-3</v>
       </c>
       <c r="K6">
         <f t="shared" si="3"/>
-        <v>-0.190847843885422</v>
+        <v>-0.67402482032775901</v>
       </c>
       <c r="L6">
         <f t="shared" si="4"/>
-        <v>-0.286252111196518</v>
+        <v>3.28068062663078E-3</v>
       </c>
       <c r="M6">
         <f t="shared" si="5"/>
-        <v>0.37134739756584201</v>
+        <v>0.96414262056350697</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>-0.148137778043747</v>
+        <v>0.81001901626586903</v>
       </c>
       <c r="B7">
-        <v>3.9881169795989999E-3</v>
+        <v>-1.86469033360481E-3</v>
       </c>
       <c r="C7">
-        <v>-1.40395248308778E-2</v>
+        <v>-0.55877524614334095</v>
       </c>
       <c r="D7">
-        <v>5.1419169176369895E-4</v>
+        <v>-5.2859843708574798E-3</v>
       </c>
       <c r="E7">
-        <v>1.4378885738551599E-2</v>
+        <v>0.26617881655693099</v>
       </c>
       <c r="F7">
-        <v>2.92063690721989E-4</v>
+        <v>-1.56343937851489E-3</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>2.92063690721989E-4</v>
+        <v>-1.56343937851489E-3</v>
       </c>
       <c r="I7">
         <f t="shared" si="1"/>
-        <v>-1.4378885738551599E-2</v>
+        <v>-0.26617881655693099</v>
       </c>
       <c r="J7">
         <f t="shared" si="2"/>
-        <v>5.1419169176369895E-4</v>
+        <v>-5.2859843708574798E-3</v>
       </c>
       <c r="K7">
         <f t="shared" si="3"/>
-        <v>-1.40395248308778E-2</v>
+        <v>-0.55877524614334095</v>
       </c>
       <c r="L7">
         <f t="shared" si="4"/>
-        <v>-3.9881169795989999E-3</v>
+        <v>1.86469033360481E-3</v>
       </c>
       <c r="M7">
         <f t="shared" si="5"/>
-        <v>-0.148137778043747</v>
+        <v>0.81001901626586903</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>-0.17866048216819799</v>
+        <v>0.41247585415840099</v>
       </c>
       <c r="B8">
-        <v>2.0677028223872199E-2</v>
+        <v>9.4631686806678804E-4</v>
       </c>
       <c r="C8">
-        <v>4.0111662819981601E-3</v>
+        <v>-0.27222990989685097</v>
       </c>
       <c r="D8">
-        <v>-2.08050152286887E-3</v>
+        <v>-2.4937090929597599E-3</v>
       </c>
       <c r="E8">
-        <v>7.0527084171772003E-3</v>
+        <v>0.12970544397830999</v>
       </c>
       <c r="F8">
-        <v>1.5791626647114799E-3</v>
+        <v>-6.0571008361876E-4</v>
       </c>
       <c r="H8">
         <f t="shared" si="0"/>
-        <v>1.5791626647114799E-3</v>
+        <v>-6.0571008361876E-4</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>-7.0527084171772003E-3</v>
+        <v>-0.12970544397830999</v>
       </c>
       <c r="J8">
         <f t="shared" si="2"/>
-        <v>-2.08050152286887E-3</v>
+        <v>-2.4937090929597599E-3</v>
       </c>
       <c r="K8">
         <f t="shared" si="3"/>
-        <v>4.0111662819981601E-3</v>
+        <v>-0.27222990989685097</v>
       </c>
       <c r="L8">
         <f t="shared" si="4"/>
-        <v>-2.0677028223872199E-2</v>
+        <v>-9.4631686806678804E-4</v>
       </c>
       <c r="M8">
         <f t="shared" si="5"/>
-        <v>-0.17866048216819799</v>
+        <v>0.41247585415840099</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>-0.179818570613861</v>
+        <v>1.3270040974021E-2</v>
       </c>
       <c r="B9">
-        <v>-1.1851854622364001E-2</v>
+        <v>1.36645883321762E-3</v>
       </c>
       <c r="C9">
-        <v>3.6321938969194902E-3</v>
+        <v>1.13668832927942E-2</v>
       </c>
       <c r="D9">
-        <v>2.9734096024185402E-3</v>
+        <v>4.0425369661534198E-5</v>
       </c>
       <c r="E9">
-        <v>7.1569895371794701E-3</v>
+        <v>4.1646137833595298E-4</v>
       </c>
       <c r="F9">
-        <v>-1.1583648156374699E-3</v>
+        <v>6.2304316088557203E-5</v>
       </c>
       <c r="H9">
         <f t="shared" si="0"/>
-        <v>-1.1583648156374699E-3</v>
+        <v>6.2304316088557203E-5</v>
       </c>
       <c r="I9">
         <f t="shared" si="1"/>
-        <v>-7.1569895371794701E-3</v>
+        <v>-4.1646137833595298E-4</v>
       </c>
       <c r="J9">
         <f t="shared" si="2"/>
-        <v>2.9734096024185402E-3</v>
+        <v>4.0425369661534198E-5</v>
       </c>
       <c r="K9">
         <f t="shared" si="3"/>
-        <v>3.6321938969194902E-3</v>
+        <v>1.13668832927942E-2</v>
       </c>
       <c r="L9">
         <f t="shared" si="4"/>
-        <v>1.1851854622364001E-2</v>
+        <v>-1.36645883321762E-3</v>
       </c>
       <c r="M9">
         <f t="shared" si="5"/>
-        <v>-0.179818570613861</v>
+        <v>1.3270040974021E-2</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>-0.105594038963318</v>
-      </c>
-      <c r="B10">
-        <v>7.4703618884086598E-4</v>
-      </c>
-      <c r="C10">
-        <v>-2.5370907038450199E-2</v>
-      </c>
-      <c r="D10">
-        <v>1.2023192830383799E-3</v>
-      </c>
-      <c r="E10">
-        <v>2.3585639894008598E-2</v>
-      </c>
-      <c r="F10">
-        <v>-3.69136687368155E-5</v>
-      </c>
       <c r="H10">
         <f t="shared" si="0"/>
-        <v>-3.69136687368155E-5</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <f t="shared" si="1"/>
-        <v>-2.3585639894008598E-2</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <f t="shared" si="2"/>
-        <v>1.2023192830383799E-3</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <f t="shared" si="3"/>
-        <v>-2.5370907038450199E-2</v>
+        <v>0</v>
       </c>
       <c r="L10">
         <f t="shared" si="4"/>
-        <v>-7.4703618884086598E-4</v>
+        <v>0</v>
       </c>
       <c r="M10">
         <f t="shared" si="5"/>
-        <v>-0.105594038963318</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>3.2090678811073303E-2</v>
-      </c>
-      <c r="B11">
-        <v>-1.0805079713463801E-2</v>
-      </c>
-      <c r="C11">
-        <v>-0.40724512934684798</v>
-      </c>
-      <c r="D11">
-        <v>5.0861202180385598E-3</v>
-      </c>
-      <c r="E11">
-        <v>9.7128830850124401E-2</v>
-      </c>
-      <c r="F11">
-        <v>2.6918570511043102E-3</v>
-      </c>
       <c r="H11">
         <f t="shared" si="0"/>
-        <v>2.6918570511043102E-3</v>
+        <v>0</v>
       </c>
       <c r="I11">
         <f t="shared" si="1"/>
-        <v>-9.7128830850124401E-2</v>
+        <v>0</v>
       </c>
       <c r="J11">
         <f t="shared" si="2"/>
-        <v>5.0861202180385598E-3</v>
+        <v>0</v>
       </c>
       <c r="K11">
         <f t="shared" si="3"/>
-        <v>-0.40724512934684798</v>
+        <v>0</v>
       </c>
       <c r="L11">
         <f t="shared" si="4"/>
-        <v>1.0805079713463801E-2</v>
+        <v>0</v>
       </c>
       <c r="M11">
         <f t="shared" si="5"/>
-        <v>3.2090678811073303E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>2.6900358498096501E-2</v>
-      </c>
-      <c r="B12">
-        <v>2.0746577531099299E-2</v>
-      </c>
-      <c r="C12">
-        <v>-0.38164517283439597</v>
-      </c>
-      <c r="D12">
-        <v>3.7218275247141703E-4</v>
-      </c>
-      <c r="E12">
-        <v>9.1151893138885498E-2</v>
-      </c>
-      <c r="F12">
-        <v>7.1417102590203303E-3</v>
-      </c>
       <c r="H12">
         <f t="shared" si="0"/>
-        <v>7.1417102590203303E-3</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <f t="shared" si="1"/>
-        <v>-9.1151893138885498E-2</v>
+        <v>0</v>
       </c>
       <c r="J12">
         <f t="shared" si="2"/>
-        <v>3.7218275247141703E-4</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <f t="shared" si="3"/>
-        <v>-0.38164517283439597</v>
+        <v>0</v>
       </c>
       <c r="L12">
         <f t="shared" si="4"/>
-        <v>-2.0746577531099299E-2</v>
+        <v>0</v>
       </c>
       <c r="M12">
         <f t="shared" si="5"/>
-        <v>2.6900358498096501E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>1.6371488571166999E-2</v>
-      </c>
-      <c r="B13">
-        <v>-3.4079838544130298E-2</v>
-      </c>
-      <c r="C13">
-        <v>-0.37443938851356501</v>
-      </c>
-      <c r="D13">
-        <v>8.5697956383228302E-3</v>
-      </c>
-      <c r="E13">
-        <v>8.8719904422759996E-2</v>
-      </c>
-      <c r="F13">
-        <v>-9.9307717755436897E-4</v>
-      </c>
       <c r="H13">
         <f t="shared" si="0"/>
-        <v>-9.9307717755436897E-4</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <f t="shared" si="1"/>
-        <v>-8.8719904422759996E-2</v>
+        <v>0</v>
       </c>
       <c r="J13">
         <f t="shared" si="2"/>
-        <v>8.5697956383228302E-3</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <f t="shared" si="3"/>
-        <v>-0.37443938851356501</v>
+        <v>0</v>
       </c>
       <c r="L13">
         <f t="shared" si="4"/>
-        <v>3.4079838544130298E-2</v>
+        <v>0</v>
       </c>
       <c r="M13">
         <f t="shared" si="5"/>
-        <v>1.6371488571166999E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>3.2927412539720501E-2</v>
-      </c>
-      <c r="B14">
-        <v>-1.31122367456555E-2</v>
-      </c>
-      <c r="C14">
-        <v>-0.41846364736557001</v>
-      </c>
-      <c r="D14">
-        <v>5.5827959440648599E-3</v>
-      </c>
-      <c r="E14">
-        <v>9.9095642566680894E-2</v>
-      </c>
-      <c r="F14">
-        <v>2.3157137911766798E-3</v>
-      </c>
       <c r="H14">
         <f t="shared" si="0"/>
-        <v>2.3157137911766798E-3</v>
+        <v>0</v>
       </c>
       <c r="I14">
         <f t="shared" si="1"/>
-        <v>-9.9095642566680894E-2</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <f t="shared" si="2"/>
-        <v>5.5827959440648599E-3</v>
+        <v>0</v>
       </c>
       <c r="K14">
         <f t="shared" si="3"/>
-        <v>-0.41846364736557001</v>
+        <v>0</v>
       </c>
       <c r="L14">
         <f t="shared" si="4"/>
-        <v>1.31122367456555E-2</v>
+        <v>0</v>
       </c>
       <c r="M14">
         <f t="shared" si="5"/>
-        <v>3.2927412539720501E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>6.8886458873748793E-2</v>
-      </c>
-      <c r="B15">
-        <v>0.67368566989898704</v>
-      </c>
-      <c r="C15">
-        <v>-0.16237765550613401</v>
-      </c>
-      <c r="D15">
-        <v>-8.8403537869453402E-2</v>
-      </c>
-      <c r="E15">
-        <v>5.2426334470510497E-2</v>
-      </c>
-      <c r="F15">
-        <v>1.2694518081843901E-3</v>
-      </c>
       <c r="H15">
         <f t="shared" si="0"/>
-        <v>1.2694518081843901E-3</v>
+        <v>0</v>
       </c>
       <c r="I15">
         <f t="shared" si="1"/>
-        <v>-5.2426334470510497E-2</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <f t="shared" si="2"/>
-        <v>-8.8403537869453402E-2</v>
+        <v>0</v>
       </c>
       <c r="K15">
         <f t="shared" si="3"/>
-        <v>-0.16237765550613401</v>
+        <v>0</v>
       </c>
       <c r="L15">
         <f t="shared" si="4"/>
-        <v>-0.67368566989898704</v>
+        <v>0</v>
       </c>
       <c r="M15">
         <f t="shared" si="5"/>
-        <v>6.8886458873748793E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>4.6903401613235501E-2</v>
-      </c>
-      <c r="B16">
-        <v>0.71704697608947798</v>
-      </c>
-      <c r="C16">
-        <v>-0.14485144615173301</v>
-      </c>
-      <c r="D16">
-        <v>-9.5036953687667805E-2</v>
-      </c>
-      <c r="E16">
-        <v>4.4000539928674698E-2</v>
-      </c>
-      <c r="F16">
-        <v>3.9274767041206403E-3</v>
-      </c>
       <c r="H16">
         <f t="shared" si="0"/>
-        <v>3.9274767041206403E-3</v>
+        <v>0</v>
       </c>
       <c r="I16">
         <f t="shared" si="1"/>
-        <v>-4.4000539928674698E-2</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <f t="shared" si="2"/>
-        <v>-9.5036953687667805E-2</v>
+        <v>0</v>
       </c>
       <c r="K16">
         <f t="shared" si="3"/>
-        <v>-0.14485144615173301</v>
+        <v>0</v>
       </c>
       <c r="L16">
         <f t="shared" si="4"/>
-        <v>-0.71704697608947798</v>
+        <v>0</v>
       </c>
       <c r="M16">
         <f t="shared" si="5"/>
-        <v>4.6903401613235501E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>5.6958615779876702E-2</v>
-      </c>
-      <c r="B17">
-        <v>0.631952583789825</v>
-      </c>
-      <c r="C17">
-        <v>-0.146904721856117</v>
-      </c>
-      <c r="D17">
-        <v>-8.1878006458282498E-2</v>
-      </c>
-      <c r="E17">
-        <v>4.5862302184104899E-2</v>
-      </c>
-      <c r="F17">
-        <v>-9.5364777371287303E-4</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H17">
         <f t="shared" si="0"/>
-        <v>-9.5364777371287303E-4</v>
+        <v>0</v>
       </c>
       <c r="I17">
         <f t="shared" si="1"/>
-        <v>-4.5862302184104899E-2</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <f t="shared" si="2"/>
-        <v>-8.1878006458282498E-2</v>
+        <v>0</v>
       </c>
       <c r="K17">
         <f t="shared" si="3"/>
-        <v>-0.146904721856117</v>
+        <v>0</v>
       </c>
       <c r="L17">
         <f t="shared" si="4"/>
-        <v>-0.631952583789825</v>
+        <v>0</v>
       </c>
       <c r="M17">
         <f t="shared" si="5"/>
-        <v>5.6958615779876702E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>9.2208802700042697E-2</v>
-      </c>
-      <c r="B18">
-        <v>0.66644299030303999</v>
-      </c>
-      <c r="C18">
-        <v>-0.18440371751785301</v>
-      </c>
-      <c r="D18">
-        <v>-8.6739368736743899E-2</v>
-      </c>
-      <c r="E18">
-        <v>6.00174702703953E-2</v>
-      </c>
-      <c r="F18">
-        <v>9.0643670409917799E-4</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H18">
         <f t="shared" si="0"/>
-        <v>9.0643670409917799E-4</v>
+        <v>0</v>
       </c>
       <c r="I18">
         <f t="shared" si="1"/>
-        <v>-6.00174702703953E-2</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <f t="shared" si="2"/>
-        <v>-8.6739368736743899E-2</v>
+        <v>0</v>
       </c>
       <c r="K18">
         <f t="shared" si="3"/>
-        <v>-0.18440371751785301</v>
+        <v>0</v>
       </c>
       <c r="L18">
         <f t="shared" si="4"/>
-        <v>-0.66644299030303999</v>
+        <v>0</v>
       </c>
       <c r="M18">
         <f t="shared" si="5"/>
-        <v>9.2208802700042697E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>-0.47338950634002702</v>
-      </c>
-      <c r="B19">
-        <v>0.81293100118637096</v>
-      </c>
-      <c r="C19">
-        <v>-0.22609874606132499</v>
-      </c>
-      <c r="D19">
-        <v>-0.15243518352508501</v>
-      </c>
-      <c r="E19">
-        <v>-8.6320064961910206E-2</v>
-      </c>
-      <c r="F19">
-        <v>-2.6597268879413599E-4</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H19">
         <f t="shared" si="0"/>
-        <v>-2.6597268879413599E-4</v>
+        <v>0</v>
       </c>
       <c r="I19">
         <f t="shared" si="1"/>
-        <v>8.6320064961910206E-2</v>
+        <v>0</v>
       </c>
       <c r="J19">
         <f t="shared" si="2"/>
-        <v>-0.15243518352508501</v>
+        <v>0</v>
       </c>
       <c r="K19">
         <f t="shared" si="3"/>
-        <v>-0.22609874606132499</v>
+        <v>0</v>
       </c>
       <c r="L19">
         <f t="shared" si="4"/>
-        <v>-0.81293100118637096</v>
+        <v>0</v>
       </c>
       <c r="M19">
         <f t="shared" si="5"/>
-        <v>-0.47338950634002702</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>-0.486432075500488</v>
-      </c>
-      <c r="B20">
-        <v>0.85305935144424405</v>
-      </c>
-      <c r="C20">
-        <v>-0.23291090130806</v>
-      </c>
-      <c r="D20">
-        <v>-0.16011224687099501</v>
-      </c>
-      <c r="E20">
-        <v>-8.8781088590621907E-2</v>
-      </c>
-      <c r="F20">
-        <v>-3.3348239958286302E-4</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H20">
         <f t="shared" si="0"/>
-        <v>-3.3348239958286302E-4</v>
+        <v>0</v>
       </c>
       <c r="I20">
         <f t="shared" si="1"/>
-        <v>8.8781088590621907E-2</v>
+        <v>0</v>
       </c>
       <c r="J20">
         <f t="shared" si="2"/>
-        <v>-0.16011224687099501</v>
+        <v>0</v>
       </c>
       <c r="K20">
         <f t="shared" si="3"/>
-        <v>-0.23291090130806</v>
+        <v>0</v>
       </c>
       <c r="L20">
         <f t="shared" si="4"/>
-        <v>-0.85305935144424405</v>
+        <v>0</v>
       </c>
       <c r="M20">
         <f t="shared" si="5"/>
-        <v>-0.486432075500488</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>-0.48660367727279702</v>
-      </c>
-      <c r="B21">
-        <v>0.74244308471679699</v>
-      </c>
-      <c r="C21">
-        <v>-0.200972050428391</v>
-      </c>
-      <c r="D21">
-        <v>-0.137546807527542</v>
-      </c>
-      <c r="E21">
-        <v>-8.8260546326637296E-2</v>
-      </c>
-      <c r="F21">
-        <v>1.3329796493053399E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H21">
         <f t="shared" si="0"/>
-        <v>1.3329796493053399E-3</v>
+        <v>0</v>
       </c>
       <c r="I21">
         <f t="shared" si="1"/>
-        <v>8.8260546326637296E-2</v>
+        <v>0</v>
       </c>
       <c r="J21">
         <f t="shared" si="2"/>
-        <v>-0.137546807527542</v>
+        <v>0</v>
       </c>
       <c r="K21">
         <f t="shared" si="3"/>
-        <v>-0.200972050428391</v>
+        <v>0</v>
       </c>
       <c r="L21">
         <f t="shared" si="4"/>
-        <v>-0.74244308471679699</v>
+        <v>0</v>
       </c>
       <c r="M21">
         <f t="shared" si="5"/>
-        <v>-0.48660367727279702</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>-0.411002337932587</v>
-      </c>
-      <c r="B22">
-        <v>0.77179682254791304</v>
-      </c>
-      <c r="C22">
-        <v>-0.191051125526428</v>
-      </c>
-      <c r="D22">
-        <v>-0.144500657916069</v>
-      </c>
-      <c r="E22">
-        <v>-7.5751185417175307E-2</v>
-      </c>
-      <c r="F22">
-        <v>-1.8139015883207299E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H22">
         <f t="shared" si="0"/>
-        <v>-1.8139015883207299E-3</v>
+        <v>0</v>
       </c>
       <c r="I22">
         <f t="shared" si="1"/>
-        <v>7.5751185417175307E-2</v>
+        <v>0</v>
       </c>
       <c r="J22">
         <f t="shared" si="2"/>
-        <v>-0.144500657916069</v>
+        <v>0</v>
       </c>
       <c r="K22">
         <f t="shared" si="3"/>
-        <v>-0.191051125526428</v>
+        <v>0</v>
       </c>
       <c r="L22">
         <f t="shared" si="4"/>
-        <v>-0.77179682254791304</v>
+        <v>0</v>
       </c>
       <c r="M22">
         <f t="shared" si="5"/>
-        <v>-0.411002337932587</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>-0.25453394651413003</v>
-      </c>
-      <c r="B23">
-        <v>0.99236428737640403</v>
-      </c>
-      <c r="C23">
-        <v>-0.18137529492378199</v>
-      </c>
-      <c r="D23">
-        <v>-0.180290177464485</v>
-      </c>
-      <c r="E23">
-        <v>-3.6083325743675197E-2</v>
-      </c>
-      <c r="F23">
-        <v>-1.1004870757460601E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H23">
         <f t="shared" si="0"/>
-        <v>-1.1004870757460601E-3</v>
+        <v>0</v>
       </c>
       <c r="I23">
         <f t="shared" si="1"/>
-        <v>3.6083325743675197E-2</v>
+        <v>0</v>
       </c>
       <c r="J23">
         <f t="shared" si="2"/>
-        <v>-0.180290177464485</v>
+        <v>0</v>
       </c>
       <c r="K23">
         <f t="shared" si="3"/>
-        <v>-0.18137529492378199</v>
+        <v>0</v>
       </c>
       <c r="L23">
         <f t="shared" si="4"/>
-        <v>-0.99236428737640403</v>
+        <v>0</v>
       </c>
       <c r="M23">
         <f t="shared" si="5"/>
-        <v>-0.25453394651413003</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>-0.286822348833084</v>
-      </c>
-      <c r="B24">
-        <v>1.0544390678405799</v>
-      </c>
-      <c r="C24">
-        <v>-0.19178026914596599</v>
-      </c>
-      <c r="D24">
-        <v>-0.19076372683048201</v>
-      </c>
-      <c r="E24">
-        <v>-4.05797101557255E-2</v>
-      </c>
-      <c r="F24">
-        <v>-7.9773366451263401E-5</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H24">
         <f t="shared" si="0"/>
-        <v>-7.9773366451263401E-5</v>
+        <v>0</v>
       </c>
       <c r="I24">
         <f t="shared" si="1"/>
-        <v>4.05797101557255E-2</v>
+        <v>0</v>
       </c>
       <c r="J24">
         <f t="shared" si="2"/>
-        <v>-0.19076372683048201</v>
+        <v>0</v>
       </c>
       <c r="K24">
         <f t="shared" si="3"/>
-        <v>-0.19178026914596599</v>
+        <v>0</v>
       </c>
       <c r="L24">
         <f t="shared" si="4"/>
-        <v>-1.0544390678405799</v>
+        <v>0</v>
       </c>
       <c r="M24">
         <f t="shared" si="5"/>
-        <v>-0.286822348833084</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>-0.26899504661560097</v>
-      </c>
-      <c r="B25">
-        <v>0.93887907266616799</v>
-      </c>
-      <c r="C25">
-        <v>-0.16189207136631001</v>
-      </c>
-      <c r="D25">
-        <v>-0.16816398501396199</v>
-      </c>
-      <c r="E25">
-        <v>-3.7795923650264698E-2</v>
-      </c>
-      <c r="F25">
-        <v>8.9275650680065196E-5</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H25">
         <f t="shared" si="0"/>
-        <v>8.9275650680065196E-5</v>
+        <v>0</v>
       </c>
       <c r="I25">
         <f t="shared" si="1"/>
-        <v>3.7795923650264698E-2</v>
+        <v>0</v>
       </c>
       <c r="J25">
         <f t="shared" si="2"/>
-        <v>-0.16816398501396199</v>
+        <v>0</v>
       </c>
       <c r="K25">
         <f t="shared" si="3"/>
-        <v>-0.16189207136631001</v>
+        <v>0</v>
       </c>
       <c r="L25">
         <f t="shared" si="4"/>
-        <v>-0.93887907266616799</v>
+        <v>0</v>
       </c>
       <c r="M25">
         <f t="shared" si="5"/>
-        <v>-0.26899504661560097</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>-0.17800956964492801</v>
-      </c>
-      <c r="B26">
-        <v>0.91853284835815396</v>
-      </c>
-      <c r="C26">
-        <v>-0.154843360185623</v>
-      </c>
-      <c r="D26">
-        <v>-0.16904753446578999</v>
-      </c>
-      <c r="E26">
-        <v>-2.5789694860577601E-2</v>
-      </c>
-      <c r="F26">
-        <v>-3.0912766233086599E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H26">
         <f t="shared" si="0"/>
-        <v>-3.0912766233086599E-3</v>
+        <v>0</v>
       </c>
       <c r="I26">
         <f t="shared" si="1"/>
-        <v>2.5789694860577601E-2</v>
+        <v>0</v>
       </c>
       <c r="J26">
         <f t="shared" si="2"/>
-        <v>-0.16904753446578999</v>
+        <v>0</v>
       </c>
       <c r="K26">
         <f t="shared" si="3"/>
-        <v>-0.154843360185623</v>
+        <v>0</v>
       </c>
       <c r="L26">
         <f t="shared" si="4"/>
-        <v>-0.91853284835815396</v>
+        <v>0</v>
       </c>
       <c r="M26">
         <f t="shared" si="5"/>
-        <v>-0.17800956964492801</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>-0.33691111207008401</v>
-      </c>
-      <c r="B27">
-        <v>0.86372590065002397</v>
-      </c>
-      <c r="C27">
-        <v>-0.45323920249938998</v>
-      </c>
-      <c r="D27">
-        <v>-0.19216823577880901</v>
-      </c>
-      <c r="E27">
-        <v>-6.0930710285902002E-2</v>
-      </c>
-      <c r="F27">
-        <v>1.21408142149448E-4</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H27">
         <f t="shared" si="0"/>
-        <v>1.21408142149448E-4</v>
+        <v>0</v>
       </c>
       <c r="I27">
         <f t="shared" si="1"/>
-        <v>6.0930710285902002E-2</v>
+        <v>0</v>
       </c>
       <c r="J27">
         <f t="shared" si="2"/>
-        <v>-0.19216823577880901</v>
+        <v>0</v>
       </c>
       <c r="K27">
         <f t="shared" si="3"/>
-        <v>-0.45323920249938998</v>
+        <v>0</v>
       </c>
       <c r="L27">
         <f t="shared" si="4"/>
-        <v>-0.86372590065002397</v>
+        <v>0</v>
       </c>
       <c r="M27">
         <f t="shared" si="5"/>
-        <v>-0.33691111207008401</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>-0.34396547079086298</v>
-      </c>
-      <c r="B28">
-        <v>0.88483870029449496</v>
-      </c>
-      <c r="C28">
-        <v>-0.469008088111877</v>
-      </c>
-      <c r="D28">
-        <v>-0.19772984087467199</v>
-      </c>
-      <c r="E28">
-        <v>-6.2060352414846399E-2</v>
-      </c>
-      <c r="F28">
-        <v>8.7325181812048002E-4</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H28">
         <f t="shared" si="0"/>
-        <v>8.7325181812048002E-4</v>
+        <v>0</v>
       </c>
       <c r="I28">
         <f t="shared" si="1"/>
-        <v>6.2060352414846399E-2</v>
+        <v>0</v>
       </c>
       <c r="J28">
         <f t="shared" si="2"/>
-        <v>-0.19772984087467199</v>
+        <v>0</v>
       </c>
       <c r="K28">
         <f t="shared" si="3"/>
-        <v>-0.469008088111877</v>
+        <v>0</v>
       </c>
       <c r="L28">
         <f t="shared" si="4"/>
-        <v>-0.88483870029449496</v>
+        <v>0</v>
       </c>
       <c r="M28">
         <f t="shared" si="5"/>
-        <v>-0.34396547079086298</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>-0.34715849161148099</v>
-      </c>
-      <c r="B29">
-        <v>0.81610763072967496</v>
-      </c>
-      <c r="C29">
-        <v>-0.42007511854171797</v>
-      </c>
-      <c r="D29">
-        <v>-0.17907203733921101</v>
-      </c>
-      <c r="E29">
-        <v>-6.2279805541038499E-2</v>
-      </c>
-      <c r="F29">
-        <v>1.88831053674221E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H29">
         <f t="shared" si="0"/>
-        <v>1.88831053674221E-3</v>
+        <v>0</v>
       </c>
       <c r="I29">
         <f t="shared" si="1"/>
-        <v>6.2279805541038499E-2</v>
+        <v>0</v>
       </c>
       <c r="J29">
         <f t="shared" si="2"/>
-        <v>-0.17907203733921101</v>
+        <v>0</v>
       </c>
       <c r="K29">
         <f t="shared" si="3"/>
-        <v>-0.42007511854171797</v>
+        <v>0</v>
       </c>
       <c r="L29">
         <f t="shared" si="4"/>
-        <v>-0.81610763072967496</v>
+        <v>0</v>
       </c>
       <c r="M29">
         <f t="shared" si="5"/>
-        <v>-0.34715849161148099</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>-0.29124367237091098</v>
-      </c>
-      <c r="B30">
-        <v>0.82586264610290505</v>
-      </c>
-      <c r="C30">
-        <v>-0.41851162910461398</v>
-      </c>
-      <c r="D30">
-        <v>-0.18414069712162001</v>
-      </c>
-      <c r="E30">
-        <v>-5.35877235233784E-2</v>
-      </c>
-      <c r="F30">
-        <v>-3.0665383674204402E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H30">
         <f t="shared" si="0"/>
-        <v>-3.0665383674204402E-3</v>
+        <v>0</v>
       </c>
       <c r="I30">
         <f t="shared" si="1"/>
-        <v>5.35877235233784E-2</v>
+        <v>0</v>
       </c>
       <c r="J30">
         <f t="shared" si="2"/>
-        <v>-0.18414069712162001</v>
+        <v>0</v>
       </c>
       <c r="K30">
         <f t="shared" si="3"/>
-        <v>-0.41851162910461398</v>
+        <v>0</v>
       </c>
       <c r="L30">
         <f t="shared" si="4"/>
-        <v>-0.82586264610290505</v>
+        <v>0</v>
       </c>
       <c r="M30">
         <f t="shared" si="5"/>
-        <v>-0.29124367237091098</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>-0.34386280179023698</v>
-      </c>
-      <c r="B31">
-        <v>1.0344259738922099</v>
-      </c>
-      <c r="C31">
-        <v>-0.44799792766571001</v>
-      </c>
-      <c r="D31">
-        <v>-0.22552120685577401</v>
-      </c>
-      <c r="E31">
-        <v>-5.3677611052990001E-2</v>
-      </c>
-      <c r="F31">
-        <v>2.0413408055901501E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H31">
         <f t="shared" si="0"/>
-        <v>2.0413408055901501E-3</v>
+        <v>0</v>
       </c>
       <c r="I31">
         <f t="shared" si="1"/>
-        <v>5.3677611052990001E-2</v>
+        <v>0</v>
       </c>
       <c r="J31">
         <f t="shared" si="2"/>
-        <v>-0.22552120685577401</v>
+        <v>0</v>
       </c>
       <c r="K31">
         <f t="shared" si="3"/>
-        <v>-0.44799792766571001</v>
+        <v>0</v>
       </c>
       <c r="L31">
         <f t="shared" si="4"/>
-        <v>-1.0344259738922099</v>
+        <v>0</v>
       </c>
       <c r="M31">
         <f t="shared" si="5"/>
-        <v>-0.34386280179023698</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>-0.34889203310012801</v>
-      </c>
-      <c r="B32">
-        <v>1.0473046302795399</v>
-      </c>
-      <c r="C32">
-        <v>-0.45064568519592302</v>
-      </c>
-      <c r="D32">
-        <v>-0.22847892343998</v>
-      </c>
-      <c r="E32">
-        <v>-5.4431032389402403E-2</v>
-      </c>
-      <c r="F32">
-        <v>3.1389072537422202E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H32">
         <f t="shared" si="0"/>
-        <v>3.1389072537422202E-3</v>
+        <v>0</v>
       </c>
       <c r="I32">
         <f t="shared" si="1"/>
-        <v>5.4431032389402403E-2</v>
+        <v>0</v>
       </c>
       <c r="J32">
         <f t="shared" si="2"/>
-        <v>-0.22847892343998</v>
+        <v>0</v>
       </c>
       <c r="K32">
         <f t="shared" si="3"/>
-        <v>-0.45064568519592302</v>
+        <v>0</v>
       </c>
       <c r="L32">
         <f t="shared" si="4"/>
-        <v>-1.0473046302795399</v>
+        <v>0</v>
       </c>
       <c r="M32">
         <f t="shared" si="5"/>
-        <v>-0.34889203310012801</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>-0.35082817077636702</v>
-      </c>
-      <c r="B33">
-        <v>0.97924649715423595</v>
-      </c>
-      <c r="C33">
-        <v>-0.41277560591697698</v>
-      </c>
-      <c r="D33">
-        <v>-0.21008741855621299</v>
-      </c>
-      <c r="E33">
-        <v>-5.4385308176279103E-2</v>
-      </c>
-      <c r="F33">
-        <v>3.9829285815358197E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H33">
         <f t="shared" si="0"/>
-        <v>3.9829285815358197E-3</v>
+        <v>0</v>
       </c>
       <c r="I33">
         <f t="shared" si="1"/>
-        <v>5.4385308176279103E-2</v>
+        <v>0</v>
       </c>
       <c r="J33">
         <f t="shared" si="2"/>
-        <v>-0.21008741855621299</v>
+        <v>0</v>
       </c>
       <c r="K33">
         <f t="shared" si="3"/>
-        <v>-0.41277560591697698</v>
+        <v>0</v>
       </c>
       <c r="L33">
         <f t="shared" si="4"/>
-        <v>-0.97924649715423595</v>
+        <v>0</v>
       </c>
       <c r="M33">
         <f t="shared" si="5"/>
-        <v>-0.35082817077636702</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>-0.29139718413353</v>
-      </c>
-      <c r="B34">
-        <v>0.99269974231720004</v>
-      </c>
-      <c r="C34">
-        <v>-0.415846437215805</v>
-      </c>
-      <c r="D34">
-        <v>-0.21646480262279499</v>
-      </c>
-      <c r="E34">
-        <v>-4.5837476849555997E-2</v>
-      </c>
-      <c r="F34">
-        <v>-1.69683527201414E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H34">
         <f t="shared" si="0"/>
-        <v>-1.69683527201414E-3</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <f t="shared" si="1"/>
-        <v>4.5837476849555997E-2</v>
+        <v>0</v>
       </c>
       <c r="J34">
         <f t="shared" si="2"/>
-        <v>-0.21646480262279499</v>
+        <v>0</v>
       </c>
       <c r="K34">
         <f t="shared" si="3"/>
-        <v>-0.415846437215805</v>
+        <v>0</v>
       </c>
       <c r="L34">
         <f t="shared" si="4"/>
-        <v>-0.99269974231720004</v>
+        <v>0</v>
       </c>
       <c r="M34">
         <f t="shared" si="5"/>
-        <v>-0.29139718413353</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>-0.25460425019264199</v>
-      </c>
-      <c r="B35">
-        <v>0.53015172481536899</v>
-      </c>
-      <c r="C35">
-        <v>-0.345878034830093</v>
-      </c>
-      <c r="D35">
-        <v>-0.130104705691338</v>
-      </c>
-      <c r="E35">
-        <v>-3.06784845888615E-2</v>
-      </c>
-      <c r="F35">
-        <v>-1.80347869172692E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H35">
         <f t="shared" si="0"/>
-        <v>-1.80347869172692E-3</v>
+        <v>0</v>
       </c>
       <c r="I35">
         <f t="shared" si="1"/>
-        <v>3.06784845888615E-2</v>
+        <v>0</v>
       </c>
       <c r="J35">
         <f t="shared" si="2"/>
-        <v>-0.130104705691338</v>
+        <v>0</v>
       </c>
       <c r="K35">
         <f t="shared" si="3"/>
-        <v>-0.345878034830093</v>
+        <v>0</v>
       </c>
       <c r="L35">
         <f t="shared" si="4"/>
-        <v>-0.53015172481536899</v>
+        <v>0</v>
       </c>
       <c r="M35">
         <f t="shared" si="5"/>
-        <v>-0.25460425019264199</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>-0.26172354817390397</v>
-      </c>
-      <c r="B36">
-        <v>0.54559373855590798</v>
-      </c>
-      <c r="C36">
-        <v>-0.36411675810813898</v>
-      </c>
-      <c r="D36">
-        <v>-0.136280506849289</v>
-      </c>
-      <c r="E36">
-        <v>-3.1845472753047901E-2</v>
-      </c>
-      <c r="F36">
-        <v>-5.9032719582319303E-4</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H36">
         <f t="shared" si="0"/>
-        <v>-5.9032719582319303E-4</v>
+        <v>0</v>
       </c>
       <c r="I36">
         <f t="shared" si="1"/>
-        <v>3.1845472753047901E-2</v>
+        <v>0</v>
       </c>
       <c r="J36">
         <f t="shared" si="2"/>
-        <v>-0.136280506849289</v>
+        <v>0</v>
       </c>
       <c r="K36">
         <f t="shared" si="3"/>
-        <v>-0.36411675810813898</v>
+        <v>0</v>
       </c>
       <c r="L36">
         <f t="shared" si="4"/>
-        <v>-0.54559373855590798</v>
+        <v>0</v>
       </c>
       <c r="M36">
         <f t="shared" si="5"/>
-        <v>-0.26172354817390397</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>-0.26288193464279203</v>
-      </c>
-      <c r="B37">
-        <v>0.50484818220138605</v>
-      </c>
-      <c r="C37">
-        <v>-0.30730828642845198</v>
-      </c>
-      <c r="D37">
-        <v>-0.118836537003517</v>
-      </c>
-      <c r="E37">
-        <v>-3.1614840030670201E-2</v>
-      </c>
-      <c r="F37">
-        <v>-4.39455267041922E-4</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H37">
         <f t="shared" si="0"/>
-        <v>-4.39455267041922E-4</v>
+        <v>0</v>
       </c>
       <c r="I37">
         <f t="shared" si="1"/>
-        <v>3.1614840030670201E-2</v>
+        <v>0</v>
       </c>
       <c r="J37">
         <f t="shared" si="2"/>
-        <v>-0.118836537003517</v>
+        <v>0</v>
       </c>
       <c r="K37">
         <f t="shared" si="3"/>
-        <v>-0.30730828642845198</v>
+        <v>0</v>
       </c>
       <c r="L37">
         <f t="shared" si="4"/>
-        <v>-0.50484818220138605</v>
+        <v>0</v>
       </c>
       <c r="M37">
         <f t="shared" si="5"/>
-        <v>-0.26288193464279203</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>-0.22978612780571001</v>
-      </c>
-      <c r="B38">
-        <v>0.51750469207763705</v>
-      </c>
-      <c r="C38">
-        <v>-0.32517495751380898</v>
-      </c>
-      <c r="D38">
-        <v>-0.12567727267742199</v>
-      </c>
-      <c r="E38">
-        <v>-2.7182761579752E-2</v>
-      </c>
-      <c r="F38">
-        <v>-5.0033815205097198E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H38">
         <f t="shared" si="0"/>
-        <v>-5.0033815205097198E-3</v>
+        <v>0</v>
       </c>
       <c r="I38">
         <f t="shared" si="1"/>
-        <v>2.7182761579752E-2</v>
+        <v>0</v>
       </c>
       <c r="J38">
         <f t="shared" si="2"/>
-        <v>-0.12567727267742199</v>
+        <v>0</v>
       </c>
       <c r="K38">
         <f t="shared" si="3"/>
-        <v>-0.32517495751380898</v>
+        <v>0</v>
       </c>
       <c r="L38">
         <f t="shared" si="4"/>
-        <v>-0.51750469207763705</v>
+        <v>0</v>
       </c>
       <c r="M38">
         <f t="shared" si="5"/>
-        <v>-0.22978612780571001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>-0.53375589847564697</v>
-      </c>
-      <c r="B39">
-        <v>6.3374787569046007E-2</v>
-      </c>
-      <c r="C39">
-        <v>-0.111510291695595</v>
-      </c>
-      <c r="D39">
-        <v>-8.7546631693839992E-3</v>
-      </c>
-      <c r="E39">
-        <v>-9.5996417105197906E-2</v>
-      </c>
-      <c r="F39">
-        <v>-9.0274820104241404E-4</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H39">
         <f t="shared" si="0"/>
-        <v>-9.0274820104241404E-4</v>
+        <v>0</v>
       </c>
       <c r="I39">
         <f t="shared" si="1"/>
-        <v>9.5996417105197906E-2</v>
+        <v>0</v>
       </c>
       <c r="J39">
         <f t="shared" si="2"/>
-        <v>-8.7546631693839992E-3</v>
+        <v>0</v>
       </c>
       <c r="K39">
         <f t="shared" si="3"/>
-        <v>-0.111510291695595</v>
+        <v>0</v>
       </c>
       <c r="L39">
         <f t="shared" si="4"/>
-        <v>-6.3374787569046007E-2</v>
+        <v>0</v>
       </c>
       <c r="M39">
         <f t="shared" si="5"/>
-        <v>-0.53375589847564697</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>-0.56326234340667702</v>
-      </c>
-      <c r="B40">
-        <v>7.4356511235237094E-2</v>
-      </c>
-      <c r="C40">
-        <v>-0.116913236677647</v>
-      </c>
-      <c r="D40">
-        <v>-1.01551841944456E-2</v>
-      </c>
-      <c r="E40">
-        <v>-0.101854160428047</v>
-      </c>
-      <c r="F40">
-        <v>-2.4800330866128202E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H40">
         <f t="shared" si="0"/>
-        <v>-2.4800330866128202E-3</v>
+        <v>0</v>
       </c>
       <c r="I40">
         <f t="shared" si="1"/>
-        <v>0.101854160428047</v>
+        <v>0</v>
       </c>
       <c r="J40">
         <f t="shared" si="2"/>
-        <v>-1.01551841944456E-2</v>
+        <v>0</v>
       </c>
       <c r="K40">
         <f t="shared" si="3"/>
-        <v>-0.116913236677647</v>
+        <v>0</v>
       </c>
       <c r="L40">
         <f t="shared" si="4"/>
-        <v>-7.4356511235237094E-2</v>
+        <v>0</v>
       </c>
       <c r="M40">
         <f t="shared" si="5"/>
-        <v>-0.56326234340667702</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>-0.51695328950882002</v>
-      </c>
-      <c r="B41">
-        <v>4.8026587814092601E-2</v>
-      </c>
-      <c r="C41">
-        <v>-0.10895030945539499</v>
-      </c>
-      <c r="D41">
-        <v>-6.8005314096808399E-3</v>
-      </c>
-      <c r="E41">
-        <v>-9.6029371023178101E-2</v>
-      </c>
-      <c r="F41">
-        <v>8.2076713442802397E-4</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H41">
         <f t="shared" si="0"/>
-        <v>8.2076713442802397E-4</v>
+        <v>0</v>
       </c>
       <c r="I41">
         <f t="shared" si="1"/>
-        <v>9.6029371023178101E-2</v>
+        <v>0</v>
       </c>
       <c r="J41">
         <f t="shared" si="2"/>
-        <v>-6.8005314096808399E-3</v>
+        <v>0</v>
       </c>
       <c r="K41">
         <f t="shared" si="3"/>
-        <v>-0.10895030945539499</v>
+        <v>0</v>
       </c>
       <c r="L41">
         <f t="shared" si="4"/>
-        <v>-4.8026587814092601E-2</v>
+        <v>0</v>
       </c>
       <c r="M41">
         <f t="shared" si="5"/>
-        <v>-0.51695328950882002</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>-0.47606992721557601</v>
-      </c>
-      <c r="B42">
-        <v>6.3276618719100994E-2</v>
-      </c>
-      <c r="C42">
-        <v>-8.9639320969581604E-2</v>
-      </c>
-      <c r="D42">
-        <v>-8.4429755806922895E-3</v>
-      </c>
-      <c r="E42">
-        <v>-8.2321278750896495E-2</v>
-      </c>
-      <c r="F42">
-        <v>-4.8528495244681803E-4</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H42">
         <f t="shared" si="0"/>
-        <v>-4.8528495244681803E-4</v>
+        <v>0</v>
       </c>
       <c r="I42">
         <f t="shared" si="1"/>
-        <v>8.2321278750896495E-2</v>
+        <v>0</v>
       </c>
       <c r="J42">
         <f t="shared" si="2"/>
-        <v>-8.4429755806922895E-3</v>
+        <v>0</v>
       </c>
       <c r="K42">
         <f t="shared" si="3"/>
-        <v>-8.9639320969581604E-2</v>
+        <v>0</v>
       </c>
       <c r="L42">
         <f t="shared" si="4"/>
-        <v>-6.3276618719100994E-2</v>
+        <v>0</v>
       </c>
       <c r="M42">
         <f t="shared" si="5"/>
-        <v>-0.47606992721557601</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>-0.87223374843597401</v>
-      </c>
-      <c r="B43">
-        <v>0.69346159696579002</v>
-      </c>
-      <c r="C43">
-        <v>-0.26385891437530501</v>
-      </c>
-      <c r="D43">
-        <v>-7.8640699386596694E-2</v>
-      </c>
-      <c r="E43">
-        <v>-0.18510913848877</v>
-      </c>
-      <c r="F43">
-        <v>7.30549916625023E-4</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H43">
         <f t="shared" si="0"/>
-        <v>7.30549916625023E-4</v>
+        <v>0</v>
       </c>
       <c r="I43">
         <f t="shared" si="1"/>
-        <v>0.18510913848877</v>
+        <v>0</v>
       </c>
       <c r="J43">
         <f t="shared" si="2"/>
-        <v>-7.8640699386596694E-2</v>
+        <v>0</v>
       </c>
       <c r="K43">
         <f t="shared" si="3"/>
-        <v>-0.26385891437530501</v>
+        <v>0</v>
       </c>
       <c r="L43">
         <f t="shared" si="4"/>
-        <v>-0.69346159696579002</v>
+        <v>0</v>
       </c>
       <c r="M43">
         <f t="shared" si="5"/>
-        <v>-0.87223374843597401</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>-0.88184249401092496</v>
-      </c>
-      <c r="B44">
-        <v>0.72528666257858299</v>
-      </c>
-      <c r="C44">
-        <v>-0.26602244377136203</v>
-      </c>
-      <c r="D44">
-        <v>-8.2940965890884399E-2</v>
-      </c>
-      <c r="E44">
-        <v>-0.187246784567833</v>
-      </c>
-      <c r="F44">
-        <v>-3.1077666208147998E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H44">
         <f t="shared" si="0"/>
-        <v>-3.1077666208147998E-3</v>
+        <v>0</v>
       </c>
       <c r="I44">
         <f t="shared" si="1"/>
-        <v>0.187246784567833</v>
+        <v>0</v>
       </c>
       <c r="J44">
         <f t="shared" si="2"/>
-        <v>-8.2940965890884399E-2</v>
+        <v>0</v>
       </c>
       <c r="K44">
         <f t="shared" si="3"/>
-        <v>-0.26602244377136203</v>
+        <v>0</v>
       </c>
       <c r="L44">
         <f t="shared" si="4"/>
-        <v>-0.72528666257858299</v>
+        <v>0</v>
       </c>
       <c r="M44">
         <f t="shared" si="5"/>
-        <v>-0.88184249401092496</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>-0.87556362152099598</v>
-      </c>
-      <c r="B45">
-        <v>0.66138935089111295</v>
-      </c>
-      <c r="C45">
-        <v>-0.26165169477462802</v>
-      </c>
-      <c r="D45">
-        <v>-7.4075989425182301E-2</v>
-      </c>
-      <c r="E45">
-        <v>-0.18550981581211101</v>
-      </c>
-      <c r="F45">
-        <v>4.3586762621998804E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H45">
         <f t="shared" si="0"/>
-        <v>4.3586762621998804E-3</v>
+        <v>0</v>
       </c>
       <c r="I45">
         <f t="shared" si="1"/>
-        <v>0.18550981581211101</v>
+        <v>0</v>
       </c>
       <c r="J45">
         <f t="shared" si="2"/>
-        <v>-7.4075989425182301E-2</v>
+        <v>0</v>
       </c>
       <c r="K45">
         <f t="shared" si="3"/>
-        <v>-0.26165169477462802</v>
+        <v>0</v>
       </c>
       <c r="L45">
         <f t="shared" si="4"/>
-        <v>-0.66138935089111295</v>
+        <v>0</v>
       </c>
       <c r="M45">
         <f t="shared" si="5"/>
-        <v>-0.87556362152099598</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>-0.80167603492736805</v>
-      </c>
-      <c r="B46">
-        <v>0.68642711639404297</v>
-      </c>
-      <c r="C46">
-        <v>-0.22837942838668801</v>
-      </c>
-      <c r="D46">
-        <v>-7.7373176813125596E-2</v>
-      </c>
-      <c r="E46">
-        <v>-0.16870972514152499</v>
-      </c>
-      <c r="F46">
-        <v>9.03414096683264E-4</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H46">
         <f t="shared" si="0"/>
-        <v>9.03414096683264E-4</v>
+        <v>0</v>
       </c>
       <c r="I46">
         <f t="shared" si="1"/>
-        <v>0.16870972514152499</v>
+        <v>0</v>
       </c>
       <c r="J46">
         <f t="shared" si="2"/>
-        <v>-7.7373176813125596E-2</v>
+        <v>0</v>
       </c>
       <c r="K46">
         <f t="shared" si="3"/>
-        <v>-0.22837942838668801</v>
+        <v>0</v>
       </c>
       <c r="L46">
         <f t="shared" si="4"/>
-        <v>-0.68642711639404297</v>
+        <v>0</v>
       </c>
       <c r="M46">
         <f t="shared" si="5"/>
-        <v>-0.80167603492736805</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>-0.29305437207222002</v>
-      </c>
-      <c r="B47">
-        <v>0.46341708302497903</v>
-      </c>
-      <c r="C47">
-        <v>-0.235873714089394</v>
-      </c>
-      <c r="D47">
-        <v>-7.0226937532424899E-2</v>
-      </c>
-      <c r="E47">
-        <v>-9.8053239285945906E-2</v>
-      </c>
-      <c r="F47">
-        <v>-2.9432689771056201E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H47">
         <f t="shared" si="0"/>
-        <v>-2.9432689771056201E-3</v>
+        <v>0</v>
       </c>
       <c r="I47">
         <f t="shared" si="1"/>
-        <v>9.8053239285945906E-2</v>
+        <v>0</v>
       </c>
       <c r="J47">
         <f t="shared" si="2"/>
-        <v>-7.0226937532424899E-2</v>
+        <v>0</v>
       </c>
       <c r="K47">
         <f t="shared" si="3"/>
-        <v>-0.235873714089394</v>
+        <v>0</v>
       </c>
       <c r="L47">
         <f t="shared" si="4"/>
-        <v>-0.46341708302497903</v>
+        <v>0</v>
       </c>
       <c r="M47">
         <f t="shared" si="5"/>
-        <v>-0.29305437207222002</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>-0.30155980587005599</v>
-      </c>
-      <c r="B48">
-        <v>0.501725673675537</v>
-      </c>
-      <c r="C48">
-        <v>-0.24268664419651001</v>
-      </c>
-      <c r="D48">
-        <v>-7.6301038265228299E-2</v>
-      </c>
-      <c r="E48">
-        <v>-0.10110595822334301</v>
-      </c>
-      <c r="F48">
-        <v>-5.5604549124836896E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H48">
         <f t="shared" si="0"/>
-        <v>-5.5604549124836896E-3</v>
+        <v>0</v>
       </c>
       <c r="I48">
         <f t="shared" si="1"/>
-        <v>0.10110595822334301</v>
+        <v>0</v>
       </c>
       <c r="J48">
         <f t="shared" si="2"/>
-        <v>-7.6301038265228299E-2</v>
+        <v>0</v>
       </c>
       <c r="K48">
         <f t="shared" si="3"/>
-        <v>-0.24268664419651001</v>
+        <v>0</v>
       </c>
       <c r="L48">
         <f t="shared" si="4"/>
-        <v>-0.501725673675537</v>
+        <v>0</v>
       </c>
       <c r="M48">
         <f t="shared" si="5"/>
-        <v>-0.30155980587005599</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>-0.30414065718650801</v>
-      </c>
-      <c r="B49">
-        <v>0.39477950334549</v>
-      </c>
-      <c r="C49">
-        <v>-0.24258817732334101</v>
-      </c>
-      <c r="D49">
-        <v>-5.9131160378456102E-2</v>
-      </c>
-      <c r="E49">
-        <v>-0.10198536515235899</v>
-      </c>
-      <c r="F49">
-        <v>1.5366636216640501E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H49">
         <f t="shared" si="0"/>
-        <v>1.5366636216640501E-3</v>
+        <v>0</v>
       </c>
       <c r="I49">
         <f t="shared" si="1"/>
-        <v>0.10198536515235899</v>
+        <v>0</v>
       </c>
       <c r="J49">
         <f t="shared" si="2"/>
-        <v>-5.9131160378456102E-2</v>
+        <v>0</v>
       </c>
       <c r="K49">
         <f t="shared" si="3"/>
-        <v>-0.24258817732334101</v>
+        <v>0</v>
       </c>
       <c r="L49">
         <f t="shared" si="4"/>
-        <v>-0.39477950334549</v>
+        <v>0</v>
       </c>
       <c r="M49">
         <f t="shared" si="5"/>
-        <v>-0.30414065718650801</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>-0.262890994548798</v>
-      </c>
-      <c r="B50">
-        <v>0.44012790918350198</v>
-      </c>
-      <c r="C50">
-        <v>-0.197530642151833</v>
-      </c>
-      <c r="D50">
-        <v>-6.6620744764804798E-2</v>
-      </c>
-      <c r="E50">
-        <v>-8.6323104798793807E-2</v>
-      </c>
-      <c r="F50">
-        <v>-2.3458977229893199E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H50">
         <f t="shared" si="0"/>
-        <v>-2.3458977229893199E-3</v>
+        <v>0</v>
       </c>
       <c r="I50">
         <f t="shared" si="1"/>
-        <v>8.6323104798793807E-2</v>
+        <v>0</v>
       </c>
       <c r="J50">
         <f t="shared" si="2"/>
-        <v>-6.6620744764804798E-2</v>
+        <v>0</v>
       </c>
       <c r="K50">
         <f t="shared" si="3"/>
-        <v>-0.197530642151833</v>
+        <v>0</v>
       </c>
       <c r="L50">
         <f t="shared" si="4"/>
-        <v>-0.44012790918350198</v>
+        <v>0</v>
       </c>
       <c r="M50">
         <f t="shared" si="5"/>
-        <v>-0.262890994548798</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>-0.91890478134155296</v>
-      </c>
-      <c r="B51">
-        <v>0.175033524632454</v>
-      </c>
-      <c r="C51">
-        <v>-0.444032043218613</v>
-      </c>
-      <c r="D51">
-        <v>-2.2679660469293601E-2</v>
-      </c>
-      <c r="E51">
-        <v>-0.193452998995781</v>
-      </c>
-      <c r="F51">
-        <v>-8.9650582522153906E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H51">
         <f t="shared" si="0"/>
-        <v>-8.9650582522153906E-3</v>
+        <v>0</v>
       </c>
       <c r="I51">
         <f t="shared" si="1"/>
-        <v>0.193452998995781</v>
+        <v>0</v>
       </c>
       <c r="J51">
         <f t="shared" si="2"/>
-        <v>-2.2679660469293601E-2</v>
+        <v>0</v>
       </c>
       <c r="K51">
         <f t="shared" si="3"/>
-        <v>-0.444032043218613</v>
+        <v>0</v>
       </c>
       <c r="L51">
         <f t="shared" si="4"/>
-        <v>-0.175033524632454</v>
+        <v>0</v>
       </c>
       <c r="M51">
         <f t="shared" si="5"/>
-        <v>-0.91890478134155296</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>-0.91903555393219005</v>
-      </c>
-      <c r="B52">
-        <v>0.198223441839218</v>
-      </c>
-      <c r="C52">
-        <v>-0.44682756066322299</v>
-      </c>
-      <c r="D52">
-        <v>-2.6282684877514801E-2</v>
-      </c>
-      <c r="E52">
-        <v>-0.19432164728641499</v>
-      </c>
-      <c r="F52">
-        <v>-1.30788292735815E-2</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H52">
         <f t="shared" si="0"/>
-        <v>-1.30788292735815E-2</v>
+        <v>0</v>
       </c>
       <c r="I52">
         <f t="shared" si="1"/>
-        <v>0.19432164728641499</v>
+        <v>0</v>
       </c>
       <c r="J52">
         <f t="shared" si="2"/>
-        <v>-2.6282684877514801E-2</v>
+        <v>0</v>
       </c>
       <c r="K52">
         <f t="shared" si="3"/>
-        <v>-0.44682756066322299</v>
+        <v>0</v>
       </c>
       <c r="L52">
         <f t="shared" si="4"/>
-        <v>-0.198223441839218</v>
+        <v>0</v>
       </c>
       <c r="M52">
         <f t="shared" si="5"/>
-        <v>-0.91903555393219005</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>-0.90540969371795699</v>
-      </c>
-      <c r="B53">
-        <v>0.14391160011291501</v>
-      </c>
-      <c r="C53">
-        <v>-0.45067426562309298</v>
-      </c>
-      <c r="D53">
-        <v>-1.7926901578903202E-2</v>
-      </c>
-      <c r="E53">
-        <v>-0.19395534694194799</v>
-      </c>
-      <c r="F53">
-        <v>-3.6557628773152798E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H53">
         <f t="shared" si="0"/>
-        <v>-3.6557628773152798E-3</v>
+        <v>0</v>
       </c>
       <c r="I53">
         <f t="shared" si="1"/>
-        <v>0.19395534694194799</v>
+        <v>0</v>
       </c>
       <c r="J53">
         <f t="shared" si="2"/>
-        <v>-1.7926901578903202E-2</v>
+        <v>0</v>
       </c>
       <c r="K53">
         <f t="shared" si="3"/>
-        <v>-0.45067426562309298</v>
+        <v>0</v>
       </c>
       <c r="L53">
         <f t="shared" si="4"/>
-        <v>-0.14391160011291501</v>
+        <v>0</v>
       </c>
       <c r="M53">
         <f t="shared" si="5"/>
-        <v>-0.90540969371795699</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>-0.87853527069091797</v>
-      </c>
-      <c r="B54">
-        <v>0.16112147271633101</v>
-      </c>
-      <c r="C54">
-        <v>-0.38894972205161998</v>
-      </c>
-      <c r="D54">
-        <v>-2.0251551643013999E-2</v>
-      </c>
-      <c r="E54">
-        <v>-0.178644955158234</v>
-      </c>
-      <c r="F54">
-        <v>-6.7889746278524399E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H54">
         <f t="shared" si="0"/>
-        <v>-6.7889746278524399E-3</v>
+        <v>0</v>
       </c>
       <c r="I54">
         <f t="shared" si="1"/>
-        <v>0.178644955158234</v>
+        <v>0</v>
       </c>
       <c r="J54">
         <f t="shared" si="2"/>
-        <v>-2.0251551643013999E-2</v>
+        <v>0</v>
       </c>
       <c r="K54">
         <f t="shared" si="3"/>
-        <v>-0.38894972205161998</v>
+        <v>0</v>
       </c>
       <c r="L54">
         <f t="shared" si="4"/>
-        <v>-0.16112147271633101</v>
+        <v>0</v>
       </c>
       <c r="M54">
         <f t="shared" si="5"/>
-        <v>-0.87853527069091797</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -15244,12 +14437,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15506,17 +14698,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -15541,18 +14743,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>